--- a/AAII_Financials/Yearly/FSV_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/FSV_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="92">
   <si>
     <t>FSV</t>
   </si>
@@ -951,7 +951,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>10000</v>
+        <v>12100</v>
       </c>
       <c r="E14" s="3">
         <v>-18800</v>
@@ -1151,8 +1151,8 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>8</v>
+      <c r="D20" s="3">
+        <v>-2100</v>
       </c>
       <c r="E20" s="3">
         <v>1200</v>
@@ -1194,7 +1194,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>535400</v>
+        <v>537500</v>
       </c>
       <c r="E21" s="3">
         <v>487200</v>
@@ -1655,8 +1655,8 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>8</v>
+      <c r="D32" s="3">
+        <v>2100</v>
       </c>
       <c r="E32" s="3">
         <v>-1200</v>
